--- a/03_langchain/チャットアプリ作成.xlsx
+++ b/03_langchain/チャットアプリ作成.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\learning_products\03_langchain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5ED202FF-9609-4C45-8A9E-575E6AA3B7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD229F59-1C24-4394-95DD-BDDE169C099E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7A0A84FE-ACC5-4FC5-95ED-3608078C4D23}"/>
   </bookViews>
@@ -43,13 +43,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1.イメージ画面</t>
-    <rPh sb="6" eb="8">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2.フォルダ構成</t>
     <rPh sb="6" eb="8">
       <t>コウセイ</t>
@@ -218,6 +211,19 @@
   </si>
   <si>
     <t>streamlit run app.py</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.イメージ画面(作成後）</t>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ゴ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -377,7 +383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -402,9 +408,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -417,13 +420,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -802,17 +802,17 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -824,692 +824,668 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="H26" s="8"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="9"/>
+        <v>4</v>
+      </c>
+      <c r="H27" s="8"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="H28" s="8"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A30" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="12"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="11"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A34" s="12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A33" s="13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A34" s="14" t="s">
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A35" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A35" s="14" t="s">
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A37" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A37" s="14" t="s">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A38" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A38" s="14" t="s">
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A39" s="12"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A40" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A40" s="14" t="s">
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A41" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A41" s="14" t="s">
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A42" s="12"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A43" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A43" s="14" t="s">
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A44" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A44" s="14" t="s">
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A45" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A45" s="14" t="s">
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A46" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A46" s="14" t="s">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A48" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A48" s="14" t="s">
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A49" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A49" s="14" t="s">
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A50" s="12"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A51" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A50" s="14"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A51" s="14" t="s">
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A52" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A52" s="14" t="s">
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A54" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A53" s="14"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A54" s="14" t="s">
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A55" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A55" s="14" t="s">
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A57" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A57" s="14" t="s">
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A58" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A58" s="14" t="s">
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="12"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A59" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A59" s="14" t="s">
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A61" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="14"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A60" s="14"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A61" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A62" s="14"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A65" s="12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A65" s="14" t="s">
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A66" s="12"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A67" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A66" s="14"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="14"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A67" s="14" t="s">
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A68" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="14"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A68" s="14" t="s">
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A69" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A69" s="14" t="s">
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A70" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A70" s="14" t="s">
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A71" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A71" s="14" t="s">
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A72" s="12"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A73" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="14"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A72" s="14"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A73" s="14" t="s">
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
+      <c r="I73" s="12"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A74" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A74" s="14" t="s">
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A75" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A75" s="14" t="s">
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A76" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="14"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A76" s="14" t="s">
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A78" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="14"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A78" s="15" t="s">
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A79" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A79" s="15" t="s">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A80" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A80" s="14" t="s">
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="12"/>
+      <c r="I80" s="12"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A81" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A81" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12"/>
+      <c r="I81" s="12"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A84" s="12" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A84" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="14"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
+      <c r="I84" s="12"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A86" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A87" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A87" s="14" t="s">
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="12"/>
+      <c r="I87" s="12"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A88" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B87" s="14"/>
-      <c r="C87" s="14"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="14"/>
-      <c r="I87" s="14"/>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A88" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B88" s="14"/>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="H88" s="14"/>
-      <c r="I88" s="14"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+      <c r="H88" s="12"/>
+      <c r="I88" s="12"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A90" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A91" s="12" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A91" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B91" s="14"/>
-      <c r="C91" s="14"/>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
-      <c r="H91" s="14"/>
-      <c r="I91" s="14"/>
+      <c r="B91" s="12"/>
+      <c r="C91" s="12"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+      <c r="H91" s="12"/>
+      <c r="I91" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
